--- a/public/downloads/emergency-budget-reset.xlsx
+++ b/public/downloads/emergency-budget-reset.xlsx
@@ -1,5 +1,13 @@
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Emergency Reset" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="4">
     <font>
@@ -100,19 +108,449 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Emergency Reset" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml>﻿<?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols><col min="1" max="1" width="10" customWidth="1"/><col min="2" max="2" width="24" customWidth="1"/><col min="3" max="3" width="16" customWidth="1"/><col min="4" max="4" width="18" customWidth="1"/><col min="5" max="5" width="14" customWidth="1"/><col min="6" max="6" width="34" customWidth="1"/><col min="7" max="7" width="24" customWidth="1"/><col min="8" max="8" width="16" customWidth="1"/><col min="9" max="9" width="30" customWidth="1"/></cols>
-  <sheetData><row r="1" ht="24" customHeight="1"><c r="A1"<c t="inlineStr" s="1"><is><t>Emergency Budget Reset Worksheet</t></is></c>.Substring(2)<c r="B1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="C1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="D1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="E1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="F1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="G1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="H1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="I1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)</row><row r="2"><c r="A2"<c t="inlineStr" s="3"><is><t>Prioritize essentials, action steps, and provider calls during a short-term cash crunch.</t></is></c>.Substring(2)<c r="B2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="C2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="D2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="E2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="F2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="G2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="H2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="I2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)</row><row r="3"><c r="A3"<c t="inlineStr" s="2"><is><t>Priority</t></is></c>.Substring(2)<c r="B3"<c t="inlineStr" s="2"><is><t>Item</t></is></c>.Substring(2)<c r="C3"<c t="inlineStr" s="2"><is><t>Amount Needed</t></is></c>.Substring(2)<c r="D3"<c t="inlineStr" s="2"><is><t>Amount Available</t></is></c>.Substring(2)<c r="E3"<c t="inlineStr" s="2"><is><t>Deadline</t></is></c>.Substring(2)<c r="F3"<c t="inlineStr" s="2"><is><t>Action Step</t></is></c>.Substring(2)<c r="G3"<c t="inlineStr" s="2"><is><t>Provider or Contact</t></is></c>.Substring(2)<c r="H3"<c t="inlineStr" s="2"><is><t>Status</t></is></c>.Substring(2)<c r="I3"<c t="inlineStr" s="2"><is><t>Notes</t></is></c>.Substring(2)</row><row r="4"><c r="A4"<c s="6"><v>1</v></c>.Substring(2)<c r="B4"<c t="inlineStr" s="6"><is><t>Food and groceries</t></is></c>.Substring(2)<c r="C4"<c s="6"><v>150</v></c>.Substring(2)<c r="D4"<c s="6"><v>75</v></c>.Substring(2)<c r="E4"<c t="inlineStr" s="6"><is><t>This week</t></is></c>.Substring(2)<c r="F4"<c t="inlineStr" s="6"><is><t>Check pantry and food resources</t></is></c>.Substring(2)<c r="G4"<c t="inlineStr" s="6"><is><t>Local pantry</t></is></c>.Substring(2)<c r="H4"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I4"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="5"><c r="A5"<c s="6"><v>2</v></c>.Substring(2)<c r="B5"<c t="inlineStr" s="6"><is><t>Housing</t></is></c>.Substring(2)<c r="C5"<c s="6"><v>1200</v></c>.Substring(2)<c r="D5"<c s="6"><v>600</v></c>.Substring(2)<c r="E5"<c t="inlineStr" s="6"><is><t>1st</t></is></c>.Substring(2)<c r="F5"<c t="inlineStr" s="6"><is><t>Contact landlord or housing agency</t></is></c>.Substring(2)<c r="G5"<c t="inlineStr" s="6"><is><t>Landlord</t></is></c>.Substring(2)<c r="H5"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I5"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="6"><c r="A6"<c s="6"><v>3</v></c>.Substring(2)<c r="B6"<c t="inlineStr" s="6"><is><t>Utilities</t></is></c>.Substring(2)<c r="C6"<c s="6"><v>180</v></c>.Substring(2)<c r="D6"<c s="6"><v>80</v></c>.Substring(2)<c r="E6"<c t="inlineStr" s="6"><is><t>10th</t></is></c>.Substring(2)<c r="F6"<c t="inlineStr" s="6"><is><t>Ask about hardship plan</t></is></c>.Substring(2)<c r="G6"<c t="inlineStr" s="6"><is><t>Utility provider</t></is></c>.Substring(2)<c r="H6"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I6"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="7"><c r="A7"<c s="6"><v>4</v></c>.Substring(2)<c r="B7"<c t="inlineStr" s="6"><is><t>Transportation</t></is></c>.Substring(2)<c r="C7"<c s="6"><v>80</v></c>.Substring(2)<c r="D7"<c s="6"><v>40</v></c>.Substring(2)<c r="E7"<c t="inlineStr" s="6"><is><t>This week</t></is></c>.Substring(2)<c r="F7"<c t="inlineStr" s="6"><is><t>Plan essential trips only</t></is></c>.Substring(2)<c r="G7"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="H7"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I7"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="8"><c r="A8"<c s="6"><v>5</v></c>.Substring(2)<c r="B8"<c t="inlineStr" s="6"><is><t>Phone or internet</t></is></c>.Substring(2)<c r="C8"<c s="6"><v>70</v></c>.Substring(2)<c r="D8"<c s="6"><v>30</v></c>.Substring(2)<c r="E8"<c t="inlineStr" s="6"><is><t>15th</t></is></c>.Substring(2)<c r="F8"<c t="inlineStr" s="6"><is><t>Ask about lower plan</t></is></c>.Substring(2)<c r="G8"<c t="inlineStr" s="6"><is><t>Provider</t></is></c>.Substring(2)<c r="H8"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I8"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="9"><c r="A9"<c s="6"><v>6</v></c>.Substring(2)<c r="B9"<c t="inlineStr" s="6"><is><t>Local assistance</t></is></c>.Substring(2)<c r="C9"<c s="6"><v>0</v></c>.Substring(2)<c r="D9"<c s="6"><v>0</v></c>.Substring(2)<c r="E9"<c t="inlineStr" s="6"><is><t>Today</t></is></c>.Substring(2)<c r="F9"<c t="inlineStr" s="6"><is><t>Call 211 or search local resources</t></is></c>.Substring(2)<c r="G9"<c t="inlineStr" s="6"><is><t>211</t></is></c>.Substring(2)<c r="H9"<c t="inlineStr" s="6"><is><t>Not started</t></is></c>.Substring(2)<c r="I9"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="10"><c r="A10"<c t="inlineStr" s="4"><is><t>Totals</t></is></c>.Substring(2)<c r="B10"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="C10"<c s="4"><f>SUM(C4:C9)</f></c>.Substring(2)<c r="D10"<c s="4"><f>SUM(D4:D9)</f></c>.Substring(2)<c r="E10"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="F10"<c t="inlineStr" s="4"><is><t>Gap to solve</t></is></c>.Substring(2)<c r="G10"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="H10"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="I10"<c s="4"><f>C10-D10</f></c>.Substring(2)</row></sheetData>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Emergency Budget Reset Worksheet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="3">
+        <is>
+          <t>Prioritize essentials, action steps, and provider calls during a short-term cash crunch.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t>Amount Needed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>Amount Available</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>Action Step</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t>Provider or Contact</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr" s="6">
+        <is>
+          <t>Food and groceries</t>
+        </is>
+      </c>
+      <c r="C4" s="6">
+        <v>150</v>
+      </c>
+      <c r="D4" s="6">
+        <v>75</v>
+      </c>
+      <c r="E4" t="inlineStr" s="6">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="6">
+        <is>
+          <t>Check pantry and food resources</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="6">
+        <is>
+          <t>Local pantry</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr" s="6">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="C5" s="6">
+        <v>1200</v>
+      </c>
+      <c r="D5" s="6">
+        <v>600</v>
+      </c>
+      <c r="E5" t="inlineStr" s="6">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="6">
+        <is>
+          <t>Contact landlord or housing agency</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="6">
+        <is>
+          <t>Landlord</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr" s="6">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C6" s="6">
+        <v>180</v>
+      </c>
+      <c r="D6" s="6">
+        <v>80</v>
+      </c>
+      <c r="E6" t="inlineStr" s="6">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="6">
+        <is>
+          <t>Ask about hardship plan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="6">
+        <is>
+          <t>Utility provider</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr" s="6">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="C7" s="6">
+        <v>80</v>
+      </c>
+      <c r="D7" s="6">
+        <v>40</v>
+      </c>
+      <c r="E7" t="inlineStr" s="6">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="6">
+        <is>
+          <t>Plan essential trips only</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr" s="6">
+        <is>
+          <t>Phone or internet</t>
+        </is>
+      </c>
+      <c r="C8" s="6">
+        <v>70</v>
+      </c>
+      <c r="D8" s="6">
+        <v>30</v>
+      </c>
+      <c r="E8" t="inlineStr" s="6">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="6">
+        <is>
+          <t>Ask about lower plan</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="6">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr" s="6">
+        <is>
+          <t>Local assistance</t>
+        </is>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr" s="6">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="6">
+        <is>
+          <t>Call 211 or search local resources</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="6">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="6">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="4">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C10" s="4">
+        <f>SUM(C4:C9)</f>
+      </c>
+      <c r="D10" s="4">
+        <f>SUM(D4:D9)</f>
+      </c>
+      <c r="E10" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="4">
+        <is>
+          <t>Gap to solve</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" s="4">
+        <f>C10-D10</f>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-
+</worksheet>
 </file>
--- a/public/downloads/emergency-budget-reset.xlsx
+++ b/public/downloads/emergency-budget-reset.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Emergency Budget Reset Worksheet</t>
   </si>
@@ -213,21 +213,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -578,7 +590,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -622,261 +634,232 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="8">
         <v>150</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="8">
         <v>75</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="8">
         <v>1200</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="8">
         <v>600</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="8">
         <v>180</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8">
         <v>80</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="8">
         <v>80</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8">
         <v>40</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="8">
         <v>70</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="8">
         <v>30</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="8">
         <v>0</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="11">
         <f>SUM(C4:C9)</f>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="11">
         <f>SUM(D4:D9)</f>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="E10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="7">
+      <c r="G10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="10">
         <f>C10-D10</f>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
